--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.793127041950569</v>
+        <v>0.7788831443169676</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6619037896906</v>
+        <v>1.895059365824723</v>
       </c>
       <c r="E2" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F2" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.12975594748242</v>
+        <v>1.646085341465892</v>
       </c>
       <c r="D3" t="n">
-        <v>13.47379663608187</v>
+        <v>2.189491953363303</v>
       </c>
       <c r="E3" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F3" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>7.234402297764666</v>
+        <v>1.175590373386758</v>
       </c>
       <c r="D4" t="n">
-        <v>8.043787802730844</v>
+        <v>1.307115517943762</v>
       </c>
       <c r="E4" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F4" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.25039671036751</v>
+        <v>2.31568946543472</v>
       </c>
       <c r="D5" t="n">
-        <v>14.30170394373008</v>
+        <v>2.324026890856138</v>
       </c>
       <c r="E5" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F5" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.633634029096768</v>
+        <v>1.402965529728225</v>
       </c>
       <c r="D6" t="n">
-        <v>3.535533905932738</v>
+        <v>0.57452425971407</v>
       </c>
       <c r="E6" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F6" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>12.36052264109243</v>
+        <v>2.008584929177521</v>
       </c>
       <c r="D7" t="n">
-        <v>12.44844101060605</v>
+        <v>2.022871664223484</v>
       </c>
       <c r="E7" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F7" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.71749558197489</v>
+        <v>2.06659303207092</v>
       </c>
       <c r="D8" t="n">
-        <v>13.01051563071747</v>
+        <v>2.114208789991589</v>
       </c>
       <c r="E8" t="n">
-        <v>3.109077410616486</v>
+        <v>0.5052250792251789</v>
       </c>
       <c r="F8" t="n">
-        <v>3.545970787572119</v>
+        <v>0.5762202529804693</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
